--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487707_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487707_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2696</v>
+        <v>1.7057</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1534</v>
+        <v>1.753</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1162</v>
+        <v>-0.0473</v>
       </c>
       <c r="G2" t="n">
         <v>1.0327</v>
@@ -610,13 +610,13 @@
         <v>0.3881</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8488</v>
+        <v>0.2849</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4856</v>
+        <v>0.0852</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3632</v>
+        <v>0.1996</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6313</v>
+        <v>0.906</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3581</v>
+        <v>2.9543</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7269</v>
+        <v>-2.0483</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1185</v>
+        <v>1.4426</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.3065</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8286</v>
+        <v>1.1362</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1137</v>
+        <v>4.2262</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3017</v>
+        <v>1.7219</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8119</v>
+        <v>2.5043</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2321</v>
+        <v>-2.7835</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5916</v>
+        <v>-1.4154</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6406</v>
+        <v>-1.3681</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0617</v>
+        <v>-0.5546</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2146</v>
+        <v>-0.1077</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.153</v>
+        <v>-0.4469</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0856</v>
+        <v>0.6397</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1535</v>
+        <v>1.5573</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2391</v>
+        <v>-0.9176</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4426</v>
+        <v>-0.1185</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3065</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1362</v>
+        <v>-0.8286</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2262</v>
+        <v>2.1137</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7219</v>
+        <v>1.3017</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5043</v>
+        <v>0.8119</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7835</v>
+        <v>-2.2321</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4154</v>
+        <v>-0.5916</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3681</v>
+        <v>-1.6406</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5462</v>
+        <v>0.0701</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9085</v>
+        <v>0.4138</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6377</v>
+        <v>-0.3437</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5642</v>
+        <v>-0.2821</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5642</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.8726</v>
+        <v>-1.99</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0425</v>
+        <v>0.7583</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8301</v>
+        <v>-2.7483</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7469</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4854</v>
+        <v>-0.6029</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9085</v>
+        <v>-0.1077</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5769</v>
+        <v>-0.4952</v>
       </c>
       <c r="V5" t="n">
         <v>0.9418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8762</v>
+        <v>-2.6487</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8585</v>
+        <v>-1.6583</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0176</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2815</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8185</v>
+        <v>-0.5911</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5157</v>
+        <v>-0.4884</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.1717</v>
+        <v>-3.8169</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.7429</v>
+        <v>-2.4426</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4289</v>
+        <v>-1.3743</v>
       </c>
       <c r="G7" t="n">
         <v>-2.2421</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.055</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7268</v>
+        <v>-0.4265</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3282</v>
+        <v>-0.2736</v>
       </c>
       <c r="V7" t="n">
         <v>0.0955</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.4191</v>
+        <v>-3.9097</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.931</v>
+        <v>-1.5306</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4881</v>
+        <v>-2.379</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2216</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4796</v>
+        <v>-0.9702</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7874</v>
+        <v>-0.387</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6922</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3299</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8118</v>
+        <v>-4.6217</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7307</v>
+        <v>-3.327</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0811</v>
+        <v>-1.2946</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.9498</v>
+        <v>-2.0729</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.0552</v>
+        <v>-1.2671</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8946</v>
+        <v>-0.8058</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.1783</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.9298</v>
+        <v>-0.6261</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2484</v>
+        <v>0.0228</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7716</v>
+        <v>-1.4696</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1254</v>
+        <v>-0.641</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6462</v>
+        <v>-0.8286</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8261</v>
+        <v>-0.5308</v>
       </c>
       <c r="T9" t="n">
-        <v>1.882</v>
+        <v>-0.1237</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0558</v>
+        <v>-0.4071</v>
       </c>
       <c r="V9" t="n">
-        <v>1.506</v>
+        <v>-0.6597</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>-0.6597</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9765</v>
+        <v>-4.6469</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6273</v>
+        <v>-1.0209</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3492</v>
+        <v>-3.626</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0729</v>
+        <v>-0.4133</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2671</v>
+        <v>-0.7036</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8058</v>
+        <v>0.2903</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6032999999999999</v>
+        <v>1.3459</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6261</v>
+        <v>0.0824</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0228</v>
+        <v>1.2635</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4696</v>
+        <v>-1.7592</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.641</v>
+        <v>-0.786</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8286</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3582</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-1.0097</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.424</v>
+        <v>-0.4265</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4616</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6597</v>
+        <v>-2.4477</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0562</v>
+        <v>-4.8412</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3212</v>
+        <v>-3.0037</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.735</v>
+        <v>-1.8375</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4133</v>
+        <v>-4.2433</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7036</v>
+        <v>-1.4294</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2903</v>
+        <v>-2.8139</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3459</v>
+        <v>-1.0487</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0824</v>
+        <v>-0.2925</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2635</v>
+        <v>-0.7562</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7592</v>
+        <v>-3.1946</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.786</v>
+        <v>-1.137</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-2.0577</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.419</v>
+        <v>-0.8516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7268</v>
+        <v>-0.2684</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6922</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4477</v>
+        <v>1.2239</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6509</v>
+        <v>-6.4585</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7044</v>
+        <v>-5.1321</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9465</v>
+        <v>-1.3264</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2433</v>
+        <v>-7.9498</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4294</v>
+        <v>-5.0552</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8139</v>
+        <v>-2.8946</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0487</v>
+        <v>-5.1783</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2925</v>
+        <v>-3.9298</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7562</v>
+        <v>-1.2484</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1946</v>
+        <v>-2.7716</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.137</v>
+        <v>-1.1254</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0577</v>
+        <v>-1.6462</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6613</v>
+        <v>0.1794</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9691</v>
+        <v>0.4806</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6922</v>
+        <v>-0.3011</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9147</v>
+        <v>-7.2521</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0201</v>
+        <v>-2.2213</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.8946</v>
+        <v>-5.0308</v>
       </c>
       <c r="G13" t="n">
         <v>-3.6071</v>
@@ -1468,13 +1468,13 @@
         <v>0.3881</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9163</v>
+        <v>-0.4212</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3358</v>
+        <v>0.1346</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4194</v>
+        <v>-0.5557</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.9344</v>
+        <v>-36.9343</v>
       </c>
       <c r="E14" t="n">
         <v>-13.3136</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.6209</v>
+        <v>-23.6205</v>
       </c>
       <c r="G14" t="n">
         <v>-23.4217</v>
@@ -1522,10 +1522,10 @@
         <v>2.9912</v>
       </c>
       <c r="K14" t="n">
-        <v>1.433599999999999</v>
+        <v>1.4336</v>
       </c>
       <c r="L14" t="n">
-        <v>1.557600000000001</v>
+        <v>1.5576</v>
       </c>
       <c r="M14" t="n">
         <v>-26.4127</v>
@@ -1546,16 +1546,16 @@
         <v>13.5823</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.6977</v>
+        <v>-5.6978</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8359000000000003</v>
+        <v>-0.8359000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.861700000000001</v>
+        <v>-4.8617</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.964100000000001</v>
+        <v>-2.9641</v>
       </c>
       <c r="W14" t="n">
         <v>2.9642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.2597</v>
+        <v>9.441599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>8.110900000000001</v>
+        <v>8.211</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1488</v>
+        <v>1.2306</v>
       </c>
       <c r="G15" t="n">
         <v>9.467499999999999</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4794</v>
+        <v>-0.2975</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0617</v>
+        <v>0.1618</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.541</v>
+        <v>-0.4593</v>
       </c>
       <c r="V15" t="n">
         <v>0.6597</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6579</v>
+        <v>6.703</v>
       </c>
       <c r="E16" t="n">
-        <v>6.9827</v>
+        <v>6.7825</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3248</v>
+        <v>-0.0795</v>
       </c>
       <c r="G16" t="n">
         <v>5.1247</v>
@@ -1702,13 +1702,13 @@
         <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6157</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2434</v>
+        <v>0.0432</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9042</v>
+        <v>-0.6589</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1886</v>
+        <v>5.0289</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4156</v>
+        <v>3.0067</v>
       </c>
       <c r="F17" t="n">
-        <v>3.773</v>
+        <v>2.0222</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1945</v>
+        <v>3.5367</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1639</v>
+        <v>3.8392</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0305</v>
+        <v>-0.3025</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4134</v>
+        <v>3.3207</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4161</v>
+        <v>3.3284</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6079</v>
+        <v>0.216</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.58</v>
+        <v>0.5108</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0279</v>
+        <v>-0.2948</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5224</v>
+        <v>2.3284</v>
       </c>
       <c r="S17" t="n">
-        <v>3.801</v>
+        <v>1.0279</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9425</v>
+        <v>0.6561</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8585</v>
+        <v>0.3718</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.844</v>
+        <v>3.3561</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4526</v>
+        <v>1.1179</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3914</v>
+        <v>2.2382</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6464</v>
+        <v>4.5873</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0068</v>
+        <v>4.3204</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3603</v>
+        <v>0.2669</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8851</v>
+        <v>5.2063</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1287</v>
+        <v>4.3665</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2436</v>
+        <v>0.8398</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2387</v>
+        <v>-0.619</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1219</v>
+        <v>-0.0462</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1168</v>
+        <v>-0.5729</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-4.8508</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3284</v>
+        <v>2.7164</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6263</v>
+        <v>0.9032</v>
       </c>
       <c r="T18" t="n">
-        <v>1.578</v>
+        <v>0.7624</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0482</v>
+        <v>0.1408</v>
       </c>
       <c r="V18" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7298</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.399</v>
+        <v>3.3158</v>
       </c>
       <c r="E19" t="n">
-        <v>2.913</v>
+        <v>1.6518</v>
       </c>
       <c r="F19" t="n">
-        <v>0.486</v>
+        <v>1.664</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0154</v>
+        <v>-0.6464</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1139</v>
+        <v>-1.0068</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0984</v>
+        <v>0.3603</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9716</v>
+        <v>-0.8851</v>
       </c>
       <c r="K19" t="n">
-        <v>0.931</v>
+        <v>-1.1287</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>0.2436</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0439</v>
+        <v>0.2387</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1829</v>
+        <v>0.1219</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.139</v>
+        <v>0.1168</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9955</v>
+        <v>1.098</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9414</v>
+        <v>0.7772</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0541</v>
+        <v>0.3208</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.7298</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.3643</v>
+        <v>3.244</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8055</v>
+        <v>2.6583</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5589</v>
+        <v>0.5857</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5367</v>
+        <v>2.8136</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8392</v>
+        <v>-0.1038</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3025</v>
+        <v>2.9174</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3207</v>
+        <v>2.5582</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3284</v>
+        <v>0.0412</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0077</v>
+        <v>2.517</v>
       </c>
       <c r="M20" t="n">
-        <v>0.216</v>
+        <v>0.2554</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5108</v>
+        <v>-0.145</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2948</v>
+        <v>0.4004</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3284</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6366000000000001</v>
+        <v>0.2364</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5451</v>
+        <v>0.1001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0915</v>
+        <v>0.1363</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.0621</v>
+        <v>2.4253</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5582</v>
+        <v>1.912</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5039</v>
+        <v>0.5132</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8136</v>
+        <v>1.0154</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1038</v>
+        <v>1.1139</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9174</v>
+        <v>-0.0984</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5582</v>
+        <v>0.9716</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0412</v>
+        <v>0.931</v>
       </c>
       <c r="L21" t="n">
-        <v>2.517</v>
+        <v>0.0406</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2554</v>
+        <v>0.0439</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.145</v>
+        <v>0.1829</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4004</v>
+        <v>-0.139</v>
       </c>
       <c r="P21" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0545</v>
+        <v>1.0218</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.9404</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0545</v>
+        <v>0.0813</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.7372</v>
+        <v>2.1336</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4172</v>
+        <v>-0.6855</v>
       </c>
       <c r="F22" t="n">
-        <v>2.32</v>
+        <v>2.8191</v>
       </c>
       <c r="G22" t="n">
-        <v>4.5873</v>
+        <v>-0.1945</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3204</v>
+        <v>-0.1639</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2669</v>
+        <v>-0.0305</v>
       </c>
       <c r="J22" t="n">
-        <v>5.2063</v>
+        <v>0.4134</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3665</v>
+        <v>0.4161</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8398</v>
+        <v>-0.0027</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.619</v>
+        <v>-0.6079</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0462</v>
+        <v>-0.58</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5729</v>
+        <v>-0.0279</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.8508</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2842</v>
+        <v>1.746</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0617</v>
+        <v>0.8414</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2226</v>
+        <v>0.9046</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>P. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.285</v>
+        <v>1.327</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4331</v>
+        <v>1.6033</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8519</v>
+        <v>-0.2763</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8548</v>
+        <v>0.2934</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8436</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0111</v>
+        <v>0.2152</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3744</v>
+        <v>0.9567</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.519</v>
+        <v>0.1854</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1446</v>
+        <v>0.7713</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4804</v>
+        <v>-0.6633</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3246</v>
+        <v>-0.1071</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1557</v>
+        <v>-0.5561</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4114</v>
+        <v>-0.2187</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2434</v>
+        <v>0.3645</v>
       </c>
       <c r="U23" t="n">
-        <v>0.168</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. VILA DE MIGUEL</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.218</v>
+        <v>1.2216</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6033</v>
+        <v>0.5332</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3853</v>
+        <v>0.6883</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2934</v>
+        <v>-0.8548</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.8436</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2152</v>
+        <v>-0.0111</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9567</v>
+        <v>-0.3744</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1854</v>
+        <v>-0.519</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7713</v>
+        <v>0.1446</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6633</v>
+        <v>-0.4804</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1071</v>
+        <v>-0.3246</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5561</v>
+        <v>-0.1557</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3277</v>
+        <v>0.348</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3645</v>
+        <v>0.3435</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6922</v>
+        <v>0.0045</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3355</v>
+        <v>0.4559</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3266</v>
+        <v>-0.726</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9911</v>
+        <v>1.1819</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5209</v>
@@ -2404,13 +2404,13 @@
         <v>1.3582</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4549</v>
+        <v>0.3365</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4845</v>
+        <v>0.1161</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0296</v>
+        <v>0.2204</v>
       </c>
       <c r="V25" t="n">
         <v>0.2821</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.7461</v>
+        <v>-1.7184</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7448</v>
+        <v>-2.4445</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9987</v>
+        <v>0.7261</v>
       </c>
       <c r="G26" t="n">
         <v>-0.2004</v>
@@ -2482,13 +2482,13 @@
         <v>0.9702</v>
       </c>
       <c r="S26" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1119</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5451</v>
+        <v>-0.2448</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6292</v>
+        <v>0.3567</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6597</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>36.9342</v>
+        <v>36.9344</v>
       </c>
       <c r="E27" t="n">
         <v>23.6207</v>
       </c>
       <c r="F27" t="n">
-        <v>13.3136</v>
+        <v>13.3135</v>
       </c>
       <c r="G27" t="n">
-        <v>23.42159999999999</v>
+        <v>23.4216</v>
       </c>
       <c r="H27" t="n">
         <v>12.6053</v>
@@ -2560,16 +2560,16 @@
         <v>18.4331</v>
       </c>
       <c r="S27" t="n">
-        <v>5.6976</v>
+        <v>5.6978</v>
       </c>
       <c r="T27" t="n">
         <v>4.8619</v>
       </c>
       <c r="U27" t="n">
-        <v>0.8358000000000001</v>
+        <v>0.8358</v>
       </c>
       <c r="V27" t="n">
-        <v>2.9643</v>
+        <v>2.964300000000001</v>
       </c>
       <c r="W27" t="n">
         <v>5.928399999999999</v>
